--- a/Data/MinionData.xlsx
+++ b/Data/MinionData.xlsx
@@ -1292,7 +1292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -1332,109 +1332,116 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>The Worker row (W) is the faction's imp. Imps read Health (max health), Strength (dig damage per second) and SkillBuild (claim/reinforce speed, 1 = normal) at their level; any of these left off the _Levels sheet keeps the imp prefab's own value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
           <t>Header cells have comments (hover) explaining each column.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
-    </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>Sheets</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Stats – master list of levelled stats: default value and whether it is a whole number. Adding a stat starts here.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>DamageTypes – master list of damage types. Column names in *_Data sheets (Dmg_&lt;ID&gt;) must match these IDs.</t>
+          <t>Stats – master list of levelled stats: default value and whether it is a whole number. Adding a stat starts here.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Abilities – one row per ability. Minion AbilityN columns hold an AbilityID from here.</t>
+          <t>DamageTypes – master list of damage types. Column names in *_Data sheets (Dmg_&lt;ID&gt;) must match these IDs.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>01U_Data – revised per-minion columns: Movement, per-damage-type multipliers, summon prerequisites.</t>
+          <t>Abilities – one row per ability. Minion AbilityN columns hold an AbilityID from here.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>01U_Levels – per-stat Min (level 1), Max (level 10), Curve and Skew. Grey L1–L10 columns are a live preview only; the game ignores them.</t>
+          <t>01U_Data – revised per-minion columns: Movement, per-damage-type multipliers, summon prerequisites.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>LevelFormula – how Curve and Skew work, with a calculator and a chart to experiment with.</t>
+          <t>01U_Levels – per-stat Min (level 1), Max (level 10), Curve and Skew. Grey L1–L10 columns are a live preview only; the game ignores them.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>LevelFormula – how Curve and Skew work, with a calculator and a chart to experiment with.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
           <t>01U_Relations – Likes/Hates cross-reference within one faction.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
-    </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>Conventions the importer would rely on</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>• Header text is the key – columns can be reordered; unknown columns are warned about, missing ones default.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>• Lists inside one cell are separated by semicolons, e.g. RoomA;RoomB</t>
+          <t>• Header text is the key – columns can be reordered; unknown columns are warned about, missing ones default.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>• Adding a stat: add a row to Stats, add it to MinionStat.cs in the game code, then add its rows to each _Levels sheet.</t>
+          <t>• Lists inside one cell are separated by semicolons, e.g. RoomA;RoomB</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>• Blank cell = default (1.0 for damage multipliers, none for prerequisites, 0 for relations).</t>
+          <t>• Adding a stat: add a row to Stats, add it to MinionStat.cs in the game code, then add its rows to each _Levels sheet.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>• Blank cell = default (1.0 for damage multipliers, none for prerequisites, 0 for relations).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>• Sheets are found by suffix (_Data, _Levels, _Relations) so per-faction pairs work fine.</t>
         </is>
@@ -3220,7 +3227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3722,6 +3729,73 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>01U</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Eidolon</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Worker</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>LandOnly</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="n"/>
+      <c r="G5" s="11" t="n"/>
+      <c r="H5" s="11" t="n"/>
+      <c r="I5" s="11" t="n"/>
+      <c r="J5" s="11" t="n"/>
+      <c r="K5" s="11" t="n"/>
+      <c r="L5" s="11" t="n"/>
+      <c r="M5" s="11" t="n"/>
+      <c r="N5" s="11" t="n"/>
+      <c r="O5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="4" t="n"/>
+      <c r="U5" s="4" t="n"/>
+      <c r="V5" s="4" t="n"/>
+      <c r="W5" s="4" t="n"/>
+      <c r="X5" s="4" t="n"/>
+      <c r="Y5" s="4" t="n"/>
+      <c r="Z5" s="4" t="n"/>
+      <c r="AA5" s="4" t="n"/>
+      <c r="AB5" s="4" t="n"/>
+      <c r="AC5" s="4" t="n"/>
+      <c r="AD5" s="4" t="n"/>
+      <c r="AE5" s="4" t="n"/>
+      <c r="AF5" s="4" t="n"/>
+      <c r="AG5" s="4" t="n"/>
+      <c r="AH5" s="4" t="n"/>
+      <c r="AI5" s="4" t="n"/>
+    </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -3742,7 +3816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q58"/>
+  <dimension ref="A1:Q77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7461,6 +7535,1189 @@
       </c>
       <c r="Q58" s="13">
         <f>IF(OR(D58="",E58=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C58,Stats!$A:$A,0)),FALSE),ROUND(D58+(E58-D58)*(1+G58)*((10-1)/(MaxLevel-1))^(2^F58),0),D58+(E58-D58)*(1+G58)*((10-1)/(MaxLevel-1))^(2^F58)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>01U</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="n"/>
+      <c r="E59" s="5" t="n"/>
+      <c r="F59" s="5" t="n"/>
+      <c r="G59" s="5" t="n"/>
+      <c r="H59" s="13">
+        <f>IF(OR(D59="",E59=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C59,Stats!$A:$A,0)),FALSE),ROUND(D59+(E59-D59)*(1+G59)*((1-1)/(MaxLevel-1))^(2^F59),0),D59+(E59-D59)*(1+G59)*((1-1)/(MaxLevel-1))^(2^F59)))</f>
+        <v/>
+      </c>
+      <c r="I59" s="13">
+        <f>IF(OR(D59="",E59=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C59,Stats!$A:$A,0)),FALSE),ROUND(D59+(E59-D59)*(1+G59)*((2-1)/(MaxLevel-1))^(2^F59),0),D59+(E59-D59)*(1+G59)*((2-1)/(MaxLevel-1))^(2^F59)))</f>
+        <v/>
+      </c>
+      <c r="J59" s="13">
+        <f>IF(OR(D59="",E59=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C59,Stats!$A:$A,0)),FALSE),ROUND(D59+(E59-D59)*(1+G59)*((3-1)/(MaxLevel-1))^(2^F59),0),D59+(E59-D59)*(1+G59)*((3-1)/(MaxLevel-1))^(2^F59)))</f>
+        <v/>
+      </c>
+      <c r="K59" s="13">
+        <f>IF(OR(D59="",E59=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C59,Stats!$A:$A,0)),FALSE),ROUND(D59+(E59-D59)*(1+G59)*((4-1)/(MaxLevel-1))^(2^F59),0),D59+(E59-D59)*(1+G59)*((4-1)/(MaxLevel-1))^(2^F59)))</f>
+        <v/>
+      </c>
+      <c r="L59" s="13">
+        <f>IF(OR(D59="",E59=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C59,Stats!$A:$A,0)),FALSE),ROUND(D59+(E59-D59)*(1+G59)*((5-1)/(MaxLevel-1))^(2^F59),0),D59+(E59-D59)*(1+G59)*((5-1)/(MaxLevel-1))^(2^F59)))</f>
+        <v/>
+      </c>
+      <c r="M59" s="13">
+        <f>IF(OR(D59="",E59=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C59,Stats!$A:$A,0)),FALSE),ROUND(D59+(E59-D59)*(1+G59)*((6-1)/(MaxLevel-1))^(2^F59),0),D59+(E59-D59)*(1+G59)*((6-1)/(MaxLevel-1))^(2^F59)))</f>
+        <v/>
+      </c>
+      <c r="N59" s="13">
+        <f>IF(OR(D59="",E59=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C59,Stats!$A:$A,0)),FALSE),ROUND(D59+(E59-D59)*(1+G59)*((7-1)/(MaxLevel-1))^(2^F59),0),D59+(E59-D59)*(1+G59)*((7-1)/(MaxLevel-1))^(2^F59)))</f>
+        <v/>
+      </c>
+      <c r="O59" s="13">
+        <f>IF(OR(D59="",E59=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C59,Stats!$A:$A,0)),FALSE),ROUND(D59+(E59-D59)*(1+G59)*((8-1)/(MaxLevel-1))^(2^F59),0),D59+(E59-D59)*(1+G59)*((8-1)/(MaxLevel-1))^(2^F59)))</f>
+        <v/>
+      </c>
+      <c r="P59" s="13">
+        <f>IF(OR(D59="",E59=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C59,Stats!$A:$A,0)),FALSE),ROUND(D59+(E59-D59)*(1+G59)*((9-1)/(MaxLevel-1))^(2^F59),0),D59+(E59-D59)*(1+G59)*((9-1)/(MaxLevel-1))^(2^F59)))</f>
+        <v/>
+      </c>
+      <c r="Q59" s="13">
+        <f>IF(OR(D59="",E59=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C59,Stats!$A:$A,0)),FALSE),ROUND(D59+(E59-D59)*(1+G59)*((10-1)/(MaxLevel-1))^(2^F59),0),D59+(E59-D59)*(1+G59)*((10-1)/(MaxLevel-1))^(2^F59)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>01U</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Salary</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="n"/>
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="5" t="n"/>
+      <c r="G60" s="5" t="n"/>
+      <c r="H60" s="13">
+        <f>IF(OR(D60="",E60=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C60,Stats!$A:$A,0)),FALSE),ROUND(D60+(E60-D60)*(1+G60)*((1-1)/(MaxLevel-1))^(2^F60),0),D60+(E60-D60)*(1+G60)*((1-1)/(MaxLevel-1))^(2^F60)))</f>
+        <v/>
+      </c>
+      <c r="I60" s="13">
+        <f>IF(OR(D60="",E60=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C60,Stats!$A:$A,0)),FALSE),ROUND(D60+(E60-D60)*(1+G60)*((2-1)/(MaxLevel-1))^(2^F60),0),D60+(E60-D60)*(1+G60)*((2-1)/(MaxLevel-1))^(2^F60)))</f>
+        <v/>
+      </c>
+      <c r="J60" s="13">
+        <f>IF(OR(D60="",E60=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C60,Stats!$A:$A,0)),FALSE),ROUND(D60+(E60-D60)*(1+G60)*((3-1)/(MaxLevel-1))^(2^F60),0),D60+(E60-D60)*(1+G60)*((3-1)/(MaxLevel-1))^(2^F60)))</f>
+        <v/>
+      </c>
+      <c r="K60" s="13">
+        <f>IF(OR(D60="",E60=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C60,Stats!$A:$A,0)),FALSE),ROUND(D60+(E60-D60)*(1+G60)*((4-1)/(MaxLevel-1))^(2^F60),0),D60+(E60-D60)*(1+G60)*((4-1)/(MaxLevel-1))^(2^F60)))</f>
+        <v/>
+      </c>
+      <c r="L60" s="13">
+        <f>IF(OR(D60="",E60=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C60,Stats!$A:$A,0)),FALSE),ROUND(D60+(E60-D60)*(1+G60)*((5-1)/(MaxLevel-1))^(2^F60),0),D60+(E60-D60)*(1+G60)*((5-1)/(MaxLevel-1))^(2^F60)))</f>
+        <v/>
+      </c>
+      <c r="M60" s="13">
+        <f>IF(OR(D60="",E60=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C60,Stats!$A:$A,0)),FALSE),ROUND(D60+(E60-D60)*(1+G60)*((6-1)/(MaxLevel-1))^(2^F60),0),D60+(E60-D60)*(1+G60)*((6-1)/(MaxLevel-1))^(2^F60)))</f>
+        <v/>
+      </c>
+      <c r="N60" s="13">
+        <f>IF(OR(D60="",E60=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C60,Stats!$A:$A,0)),FALSE),ROUND(D60+(E60-D60)*(1+G60)*((7-1)/(MaxLevel-1))^(2^F60),0),D60+(E60-D60)*(1+G60)*((7-1)/(MaxLevel-1))^(2^F60)))</f>
+        <v/>
+      </c>
+      <c r="O60" s="13">
+        <f>IF(OR(D60="",E60=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C60,Stats!$A:$A,0)),FALSE),ROUND(D60+(E60-D60)*(1+G60)*((8-1)/(MaxLevel-1))^(2^F60),0),D60+(E60-D60)*(1+G60)*((8-1)/(MaxLevel-1))^(2^F60)))</f>
+        <v/>
+      </c>
+      <c r="P60" s="13">
+        <f>IF(OR(D60="",E60=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C60,Stats!$A:$A,0)),FALSE),ROUND(D60+(E60-D60)*(1+G60)*((9-1)/(MaxLevel-1))^(2^F60),0),D60+(E60-D60)*(1+G60)*((9-1)/(MaxLevel-1))^(2^F60)))</f>
+        <v/>
+      </c>
+      <c r="Q60" s="13">
+        <f>IF(OR(D60="",E60=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C60,Stats!$A:$A,0)),FALSE),ROUND(D60+(E60-D60)*(1+G60)*((10-1)/(MaxLevel-1))^(2^F60),0),D60+(E60-D60)*(1+G60)*((10-1)/(MaxLevel-1))^(2^F60)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>01U</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="13">
+        <f>IF(OR(D61="",E61=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C61,Stats!$A:$A,0)),FALSE),ROUND(D61+(E61-D61)*(1+G61)*((1-1)/(MaxLevel-1))^(2^F61),0),D61+(E61-D61)*(1+G61)*((1-1)/(MaxLevel-1))^(2^F61)))</f>
+        <v/>
+      </c>
+      <c r="I61" s="13">
+        <f>IF(OR(D61="",E61=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C61,Stats!$A:$A,0)),FALSE),ROUND(D61+(E61-D61)*(1+G61)*((2-1)/(MaxLevel-1))^(2^F61),0),D61+(E61-D61)*(1+G61)*((2-1)/(MaxLevel-1))^(2^F61)))</f>
+        <v/>
+      </c>
+      <c r="J61" s="13">
+        <f>IF(OR(D61="",E61=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C61,Stats!$A:$A,0)),FALSE),ROUND(D61+(E61-D61)*(1+G61)*((3-1)/(MaxLevel-1))^(2^F61),0),D61+(E61-D61)*(1+G61)*((3-1)/(MaxLevel-1))^(2^F61)))</f>
+        <v/>
+      </c>
+      <c r="K61" s="13">
+        <f>IF(OR(D61="",E61=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C61,Stats!$A:$A,0)),FALSE),ROUND(D61+(E61-D61)*(1+G61)*((4-1)/(MaxLevel-1))^(2^F61),0),D61+(E61-D61)*(1+G61)*((4-1)/(MaxLevel-1))^(2^F61)))</f>
+        <v/>
+      </c>
+      <c r="L61" s="13">
+        <f>IF(OR(D61="",E61=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C61,Stats!$A:$A,0)),FALSE),ROUND(D61+(E61-D61)*(1+G61)*((5-1)/(MaxLevel-1))^(2^F61),0),D61+(E61-D61)*(1+G61)*((5-1)/(MaxLevel-1))^(2^F61)))</f>
+        <v/>
+      </c>
+      <c r="M61" s="13">
+        <f>IF(OR(D61="",E61=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C61,Stats!$A:$A,0)),FALSE),ROUND(D61+(E61-D61)*(1+G61)*((6-1)/(MaxLevel-1))^(2^F61),0),D61+(E61-D61)*(1+G61)*((6-1)/(MaxLevel-1))^(2^F61)))</f>
+        <v/>
+      </c>
+      <c r="N61" s="13">
+        <f>IF(OR(D61="",E61=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C61,Stats!$A:$A,0)),FALSE),ROUND(D61+(E61-D61)*(1+G61)*((7-1)/(MaxLevel-1))^(2^F61),0),D61+(E61-D61)*(1+G61)*((7-1)/(MaxLevel-1))^(2^F61)))</f>
+        <v/>
+      </c>
+      <c r="O61" s="13">
+        <f>IF(OR(D61="",E61=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C61,Stats!$A:$A,0)),FALSE),ROUND(D61+(E61-D61)*(1+G61)*((8-1)/(MaxLevel-1))^(2^F61),0),D61+(E61-D61)*(1+G61)*((8-1)/(MaxLevel-1))^(2^F61)))</f>
+        <v/>
+      </c>
+      <c r="P61" s="13">
+        <f>IF(OR(D61="",E61=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C61,Stats!$A:$A,0)),FALSE),ROUND(D61+(E61-D61)*(1+G61)*((9-1)/(MaxLevel-1))^(2^F61),0),D61+(E61-D61)*(1+G61)*((9-1)/(MaxLevel-1))^(2^F61)))</f>
+        <v/>
+      </c>
+      <c r="Q61" s="13">
+        <f>IF(OR(D61="",E61=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C61,Stats!$A:$A,0)),FALSE),ROUND(D61+(E61-D61)*(1+G61)*((10-1)/(MaxLevel-1))^(2^F61),0),D61+(E61-D61)*(1+G61)*((10-1)/(MaxLevel-1))^(2^F61)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>01U</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>Strength</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="13">
+        <f>IF(OR(D62="",E62=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C62,Stats!$A:$A,0)),FALSE),ROUND(D62+(E62-D62)*(1+G62)*((1-1)/(MaxLevel-1))^(2^F62),0),D62+(E62-D62)*(1+G62)*((1-1)/(MaxLevel-1))^(2^F62)))</f>
+        <v/>
+      </c>
+      <c r="I62" s="13">
+        <f>IF(OR(D62="",E62=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C62,Stats!$A:$A,0)),FALSE),ROUND(D62+(E62-D62)*(1+G62)*((2-1)/(MaxLevel-1))^(2^F62),0),D62+(E62-D62)*(1+G62)*((2-1)/(MaxLevel-1))^(2^F62)))</f>
+        <v/>
+      </c>
+      <c r="J62" s="13">
+        <f>IF(OR(D62="",E62=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C62,Stats!$A:$A,0)),FALSE),ROUND(D62+(E62-D62)*(1+G62)*((3-1)/(MaxLevel-1))^(2^F62),0),D62+(E62-D62)*(1+G62)*((3-1)/(MaxLevel-1))^(2^F62)))</f>
+        <v/>
+      </c>
+      <c r="K62" s="13">
+        <f>IF(OR(D62="",E62=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C62,Stats!$A:$A,0)),FALSE),ROUND(D62+(E62-D62)*(1+G62)*((4-1)/(MaxLevel-1))^(2^F62),0),D62+(E62-D62)*(1+G62)*((4-1)/(MaxLevel-1))^(2^F62)))</f>
+        <v/>
+      </c>
+      <c r="L62" s="13">
+        <f>IF(OR(D62="",E62=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C62,Stats!$A:$A,0)),FALSE),ROUND(D62+(E62-D62)*(1+G62)*((5-1)/(MaxLevel-1))^(2^F62),0),D62+(E62-D62)*(1+G62)*((5-1)/(MaxLevel-1))^(2^F62)))</f>
+        <v/>
+      </c>
+      <c r="M62" s="13">
+        <f>IF(OR(D62="",E62=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C62,Stats!$A:$A,0)),FALSE),ROUND(D62+(E62-D62)*(1+G62)*((6-1)/(MaxLevel-1))^(2^F62),0),D62+(E62-D62)*(1+G62)*((6-1)/(MaxLevel-1))^(2^F62)))</f>
+        <v/>
+      </c>
+      <c r="N62" s="13">
+        <f>IF(OR(D62="",E62=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C62,Stats!$A:$A,0)),FALSE),ROUND(D62+(E62-D62)*(1+G62)*((7-1)/(MaxLevel-1))^(2^F62),0),D62+(E62-D62)*(1+G62)*((7-1)/(MaxLevel-1))^(2^F62)))</f>
+        <v/>
+      </c>
+      <c r="O62" s="13">
+        <f>IF(OR(D62="",E62=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C62,Stats!$A:$A,0)),FALSE),ROUND(D62+(E62-D62)*(1+G62)*((8-1)/(MaxLevel-1))^(2^F62),0),D62+(E62-D62)*(1+G62)*((8-1)/(MaxLevel-1))^(2^F62)))</f>
+        <v/>
+      </c>
+      <c r="P62" s="13">
+        <f>IF(OR(D62="",E62=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C62,Stats!$A:$A,0)),FALSE),ROUND(D62+(E62-D62)*(1+G62)*((9-1)/(MaxLevel-1))^(2^F62),0),D62+(E62-D62)*(1+G62)*((9-1)/(MaxLevel-1))^(2^F62)))</f>
+        <v/>
+      </c>
+      <c r="Q62" s="13">
+        <f>IF(OR(D62="",E62=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C62,Stats!$A:$A,0)),FALSE),ROUND(D62+(E62-D62)*(1+G62)*((10-1)/(MaxLevel-1))^(2^F62),0),D62+(E62-D62)*(1+G62)*((10-1)/(MaxLevel-1))^(2^F62)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>01U</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="n"/>
+      <c r="E63" s="5" t="n"/>
+      <c r="F63" s="5" t="n"/>
+      <c r="G63" s="5" t="n"/>
+      <c r="H63" s="13">
+        <f>IF(OR(D63="",E63=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C63,Stats!$A:$A,0)),FALSE),ROUND(D63+(E63-D63)*(1+G63)*((1-1)/(MaxLevel-1))^(2^F63),0),D63+(E63-D63)*(1+G63)*((1-1)/(MaxLevel-1))^(2^F63)))</f>
+        <v/>
+      </c>
+      <c r="I63" s="13">
+        <f>IF(OR(D63="",E63=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C63,Stats!$A:$A,0)),FALSE),ROUND(D63+(E63-D63)*(1+G63)*((2-1)/(MaxLevel-1))^(2^F63),0),D63+(E63-D63)*(1+G63)*((2-1)/(MaxLevel-1))^(2^F63)))</f>
+        <v/>
+      </c>
+      <c r="J63" s="13">
+        <f>IF(OR(D63="",E63=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C63,Stats!$A:$A,0)),FALSE),ROUND(D63+(E63-D63)*(1+G63)*((3-1)/(MaxLevel-1))^(2^F63),0),D63+(E63-D63)*(1+G63)*((3-1)/(MaxLevel-1))^(2^F63)))</f>
+        <v/>
+      </c>
+      <c r="K63" s="13">
+        <f>IF(OR(D63="",E63=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C63,Stats!$A:$A,0)),FALSE),ROUND(D63+(E63-D63)*(1+G63)*((4-1)/(MaxLevel-1))^(2^F63),0),D63+(E63-D63)*(1+G63)*((4-1)/(MaxLevel-1))^(2^F63)))</f>
+        <v/>
+      </c>
+      <c r="L63" s="13">
+        <f>IF(OR(D63="",E63=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C63,Stats!$A:$A,0)),FALSE),ROUND(D63+(E63-D63)*(1+G63)*((5-1)/(MaxLevel-1))^(2^F63),0),D63+(E63-D63)*(1+G63)*((5-1)/(MaxLevel-1))^(2^F63)))</f>
+        <v/>
+      </c>
+      <c r="M63" s="13">
+        <f>IF(OR(D63="",E63=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C63,Stats!$A:$A,0)),FALSE),ROUND(D63+(E63-D63)*(1+G63)*((6-1)/(MaxLevel-1))^(2^F63),0),D63+(E63-D63)*(1+G63)*((6-1)/(MaxLevel-1))^(2^F63)))</f>
+        <v/>
+      </c>
+      <c r="N63" s="13">
+        <f>IF(OR(D63="",E63=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C63,Stats!$A:$A,0)),FALSE),ROUND(D63+(E63-D63)*(1+G63)*((7-1)/(MaxLevel-1))^(2^F63),0),D63+(E63-D63)*(1+G63)*((7-1)/(MaxLevel-1))^(2^F63)))</f>
+        <v/>
+      </c>
+      <c r="O63" s="13">
+        <f>IF(OR(D63="",E63=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C63,Stats!$A:$A,0)),FALSE),ROUND(D63+(E63-D63)*(1+G63)*((8-1)/(MaxLevel-1))^(2^F63),0),D63+(E63-D63)*(1+G63)*((8-1)/(MaxLevel-1))^(2^F63)))</f>
+        <v/>
+      </c>
+      <c r="P63" s="13">
+        <f>IF(OR(D63="",E63=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C63,Stats!$A:$A,0)),FALSE),ROUND(D63+(E63-D63)*(1+G63)*((9-1)/(MaxLevel-1))^(2^F63),0),D63+(E63-D63)*(1+G63)*((9-1)/(MaxLevel-1))^(2^F63)))</f>
+        <v/>
+      </c>
+      <c r="Q63" s="13">
+        <f>IF(OR(D63="",E63=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C63,Stats!$A:$A,0)),FALSE),ROUND(D63+(E63-D63)*(1+G63)*((10-1)/(MaxLevel-1))^(2^F63),0),D63+(E63-D63)*(1+G63)*((10-1)/(MaxLevel-1))^(2^F63)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>01U</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Dexterity</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="n"/>
+      <c r="E64" s="5" t="n"/>
+      <c r="F64" s="5" t="n"/>
+      <c r="G64" s="5" t="n"/>
+      <c r="H64" s="13">
+        <f>IF(OR(D64="",E64=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C64,Stats!$A:$A,0)),FALSE),ROUND(D64+(E64-D64)*(1+G64)*((1-1)/(MaxLevel-1))^(2^F64),0),D64+(E64-D64)*(1+G64)*((1-1)/(MaxLevel-1))^(2^F64)))</f>
+        <v/>
+      </c>
+      <c r="I64" s="13">
+        <f>IF(OR(D64="",E64=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C64,Stats!$A:$A,0)),FALSE),ROUND(D64+(E64-D64)*(1+G64)*((2-1)/(MaxLevel-1))^(2^F64),0),D64+(E64-D64)*(1+G64)*((2-1)/(MaxLevel-1))^(2^F64)))</f>
+        <v/>
+      </c>
+      <c r="J64" s="13">
+        <f>IF(OR(D64="",E64=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C64,Stats!$A:$A,0)),FALSE),ROUND(D64+(E64-D64)*(1+G64)*((3-1)/(MaxLevel-1))^(2^F64),0),D64+(E64-D64)*(1+G64)*((3-1)/(MaxLevel-1))^(2^F64)))</f>
+        <v/>
+      </c>
+      <c r="K64" s="13">
+        <f>IF(OR(D64="",E64=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C64,Stats!$A:$A,0)),FALSE),ROUND(D64+(E64-D64)*(1+G64)*((4-1)/(MaxLevel-1))^(2^F64),0),D64+(E64-D64)*(1+G64)*((4-1)/(MaxLevel-1))^(2^F64)))</f>
+        <v/>
+      </c>
+      <c r="L64" s="13">
+        <f>IF(OR(D64="",E64=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C64,Stats!$A:$A,0)),FALSE),ROUND(D64+(E64-D64)*(1+G64)*((5-1)/(MaxLevel-1))^(2^F64),0),D64+(E64-D64)*(1+G64)*((5-1)/(MaxLevel-1))^(2^F64)))</f>
+        <v/>
+      </c>
+      <c r="M64" s="13">
+        <f>IF(OR(D64="",E64=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C64,Stats!$A:$A,0)),FALSE),ROUND(D64+(E64-D64)*(1+G64)*((6-1)/(MaxLevel-1))^(2^F64),0),D64+(E64-D64)*(1+G64)*((6-1)/(MaxLevel-1))^(2^F64)))</f>
+        <v/>
+      </c>
+      <c r="N64" s="13">
+        <f>IF(OR(D64="",E64=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C64,Stats!$A:$A,0)),FALSE),ROUND(D64+(E64-D64)*(1+G64)*((7-1)/(MaxLevel-1))^(2^F64),0),D64+(E64-D64)*(1+G64)*((7-1)/(MaxLevel-1))^(2^F64)))</f>
+        <v/>
+      </c>
+      <c r="O64" s="13">
+        <f>IF(OR(D64="",E64=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C64,Stats!$A:$A,0)),FALSE),ROUND(D64+(E64-D64)*(1+G64)*((8-1)/(MaxLevel-1))^(2^F64),0),D64+(E64-D64)*(1+G64)*((8-1)/(MaxLevel-1))^(2^F64)))</f>
+        <v/>
+      </c>
+      <c r="P64" s="13">
+        <f>IF(OR(D64="",E64=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C64,Stats!$A:$A,0)),FALSE),ROUND(D64+(E64-D64)*(1+G64)*((9-1)/(MaxLevel-1))^(2^F64),0),D64+(E64-D64)*(1+G64)*((9-1)/(MaxLevel-1))^(2^F64)))</f>
+        <v/>
+      </c>
+      <c r="Q64" s="13">
+        <f>IF(OR(D64="",E64=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C64,Stats!$A:$A,0)),FALSE),ROUND(D64+(E64-D64)*(1+G64)*((10-1)/(MaxLevel-1))^(2^F64),0),D64+(E64-D64)*(1+G64)*((10-1)/(MaxLevel-1))^(2^F64)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>01U</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Fortitude</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="n"/>
+      <c r="E65" s="5" t="n"/>
+      <c r="F65" s="5" t="n"/>
+      <c r="G65" s="5" t="n"/>
+      <c r="H65" s="13">
+        <f>IF(OR(D65="",E65=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C65,Stats!$A:$A,0)),FALSE),ROUND(D65+(E65-D65)*(1+G65)*((1-1)/(MaxLevel-1))^(2^F65),0),D65+(E65-D65)*(1+G65)*((1-1)/(MaxLevel-1))^(2^F65)))</f>
+        <v/>
+      </c>
+      <c r="I65" s="13">
+        <f>IF(OR(D65="",E65=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C65,Stats!$A:$A,0)),FALSE),ROUND(D65+(E65-D65)*(1+G65)*((2-1)/(MaxLevel-1))^(2^F65),0),D65+(E65-D65)*(1+G65)*((2-1)/(MaxLevel-1))^(2^F65)))</f>
+        <v/>
+      </c>
+      <c r="J65" s="13">
+        <f>IF(OR(D65="",E65=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C65,Stats!$A:$A,0)),FALSE),ROUND(D65+(E65-D65)*(1+G65)*((3-1)/(MaxLevel-1))^(2^F65),0),D65+(E65-D65)*(1+G65)*((3-1)/(MaxLevel-1))^(2^F65)))</f>
+        <v/>
+      </c>
+      <c r="K65" s="13">
+        <f>IF(OR(D65="",E65=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C65,Stats!$A:$A,0)),FALSE),ROUND(D65+(E65-D65)*(1+G65)*((4-1)/(MaxLevel-1))^(2^F65),0),D65+(E65-D65)*(1+G65)*((4-1)/(MaxLevel-1))^(2^F65)))</f>
+        <v/>
+      </c>
+      <c r="L65" s="13">
+        <f>IF(OR(D65="",E65=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C65,Stats!$A:$A,0)),FALSE),ROUND(D65+(E65-D65)*(1+G65)*((5-1)/(MaxLevel-1))^(2^F65),0),D65+(E65-D65)*(1+G65)*((5-1)/(MaxLevel-1))^(2^F65)))</f>
+        <v/>
+      </c>
+      <c r="M65" s="13">
+        <f>IF(OR(D65="",E65=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C65,Stats!$A:$A,0)),FALSE),ROUND(D65+(E65-D65)*(1+G65)*((6-1)/(MaxLevel-1))^(2^F65),0),D65+(E65-D65)*(1+G65)*((6-1)/(MaxLevel-1))^(2^F65)))</f>
+        <v/>
+      </c>
+      <c r="N65" s="13">
+        <f>IF(OR(D65="",E65=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C65,Stats!$A:$A,0)),FALSE),ROUND(D65+(E65-D65)*(1+G65)*((7-1)/(MaxLevel-1))^(2^F65),0),D65+(E65-D65)*(1+G65)*((7-1)/(MaxLevel-1))^(2^F65)))</f>
+        <v/>
+      </c>
+      <c r="O65" s="13">
+        <f>IF(OR(D65="",E65=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C65,Stats!$A:$A,0)),FALSE),ROUND(D65+(E65-D65)*(1+G65)*((8-1)/(MaxLevel-1))^(2^F65),0),D65+(E65-D65)*(1+G65)*((8-1)/(MaxLevel-1))^(2^F65)))</f>
+        <v/>
+      </c>
+      <c r="P65" s="13">
+        <f>IF(OR(D65="",E65=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C65,Stats!$A:$A,0)),FALSE),ROUND(D65+(E65-D65)*(1+G65)*((9-1)/(MaxLevel-1))^(2^F65),0),D65+(E65-D65)*(1+G65)*((9-1)/(MaxLevel-1))^(2^F65)))</f>
+        <v/>
+      </c>
+      <c r="Q65" s="13">
+        <f>IF(OR(D65="",E65=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C65,Stats!$A:$A,0)),FALSE),ROUND(D65+(E65-D65)*(1+G65)*((10-1)/(MaxLevel-1))^(2^F65),0),D65+(E65-D65)*(1+G65)*((10-1)/(MaxLevel-1))^(2^F65)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>01U</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="n"/>
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" s="5" t="n"/>
+      <c r="G66" s="5" t="n"/>
+      <c r="H66" s="13">
+        <f>IF(OR(D66="",E66=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C66,Stats!$A:$A,0)),FALSE),ROUND(D66+(E66-D66)*(1+G66)*((1-1)/(MaxLevel-1))^(2^F66),0),D66+(E66-D66)*(1+G66)*((1-1)/(MaxLevel-1))^(2^F66)))</f>
+        <v/>
+      </c>
+      <c r="I66" s="13">
+        <f>IF(OR(D66="",E66=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C66,Stats!$A:$A,0)),FALSE),ROUND(D66+(E66-D66)*(1+G66)*((2-1)/(MaxLevel-1))^(2^F66),0),D66+(E66-D66)*(1+G66)*((2-1)/(MaxLevel-1))^(2^F66)))</f>
+        <v/>
+      </c>
+      <c r="J66" s="13">
+        <f>IF(OR(D66="",E66=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C66,Stats!$A:$A,0)),FALSE),ROUND(D66+(E66-D66)*(1+G66)*((3-1)/(MaxLevel-1))^(2^F66),0),D66+(E66-D66)*(1+G66)*((3-1)/(MaxLevel-1))^(2^F66)))</f>
+        <v/>
+      </c>
+      <c r="K66" s="13">
+        <f>IF(OR(D66="",E66=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C66,Stats!$A:$A,0)),FALSE),ROUND(D66+(E66-D66)*(1+G66)*((4-1)/(MaxLevel-1))^(2^F66),0),D66+(E66-D66)*(1+G66)*((4-1)/(MaxLevel-1))^(2^F66)))</f>
+        <v/>
+      </c>
+      <c r="L66" s="13">
+        <f>IF(OR(D66="",E66=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C66,Stats!$A:$A,0)),FALSE),ROUND(D66+(E66-D66)*(1+G66)*((5-1)/(MaxLevel-1))^(2^F66),0),D66+(E66-D66)*(1+G66)*((5-1)/(MaxLevel-1))^(2^F66)))</f>
+        <v/>
+      </c>
+      <c r="M66" s="13">
+        <f>IF(OR(D66="",E66=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C66,Stats!$A:$A,0)),FALSE),ROUND(D66+(E66-D66)*(1+G66)*((6-1)/(MaxLevel-1))^(2^F66),0),D66+(E66-D66)*(1+G66)*((6-1)/(MaxLevel-1))^(2^F66)))</f>
+        <v/>
+      </c>
+      <c r="N66" s="13">
+        <f>IF(OR(D66="",E66=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C66,Stats!$A:$A,0)),FALSE),ROUND(D66+(E66-D66)*(1+G66)*((7-1)/(MaxLevel-1))^(2^F66),0),D66+(E66-D66)*(1+G66)*((7-1)/(MaxLevel-1))^(2^F66)))</f>
+        <v/>
+      </c>
+      <c r="O66" s="13">
+        <f>IF(OR(D66="",E66=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C66,Stats!$A:$A,0)),FALSE),ROUND(D66+(E66-D66)*(1+G66)*((8-1)/(MaxLevel-1))^(2^F66),0),D66+(E66-D66)*(1+G66)*((8-1)/(MaxLevel-1))^(2^F66)))</f>
+        <v/>
+      </c>
+      <c r="P66" s="13">
+        <f>IF(OR(D66="",E66=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C66,Stats!$A:$A,0)),FALSE),ROUND(D66+(E66-D66)*(1+G66)*((9-1)/(MaxLevel-1))^(2^F66),0),D66+(E66-D66)*(1+G66)*((9-1)/(MaxLevel-1))^(2^F66)))</f>
+        <v/>
+      </c>
+      <c r="Q66" s="13">
+        <f>IF(OR(D66="",E66=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C66,Stats!$A:$A,0)),FALSE),ROUND(D66+(E66-D66)*(1+G66)*((10-1)/(MaxLevel-1))^(2^F66),0),D66+(E66-D66)*(1+G66)*((10-1)/(MaxLevel-1))^(2^F66)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>01U</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="n"/>
+      <c r="E67" s="5" t="n"/>
+      <c r="F67" s="5" t="n"/>
+      <c r="G67" s="5" t="n"/>
+      <c r="H67" s="13">
+        <f>IF(OR(D67="",E67=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C67,Stats!$A:$A,0)),FALSE),ROUND(D67+(E67-D67)*(1+G67)*((1-1)/(MaxLevel-1))^(2^F67),0),D67+(E67-D67)*(1+G67)*((1-1)/(MaxLevel-1))^(2^F67)))</f>
+        <v/>
+      </c>
+      <c r="I67" s="13">
+        <f>IF(OR(D67="",E67=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C67,Stats!$A:$A,0)),FALSE),ROUND(D67+(E67-D67)*(1+G67)*((2-1)/(MaxLevel-1))^(2^F67),0),D67+(E67-D67)*(1+G67)*((2-1)/(MaxLevel-1))^(2^F67)))</f>
+        <v/>
+      </c>
+      <c r="J67" s="13">
+        <f>IF(OR(D67="",E67=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C67,Stats!$A:$A,0)),FALSE),ROUND(D67+(E67-D67)*(1+G67)*((3-1)/(MaxLevel-1))^(2^F67),0),D67+(E67-D67)*(1+G67)*((3-1)/(MaxLevel-1))^(2^F67)))</f>
+        <v/>
+      </c>
+      <c r="K67" s="13">
+        <f>IF(OR(D67="",E67=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C67,Stats!$A:$A,0)),FALSE),ROUND(D67+(E67-D67)*(1+G67)*((4-1)/(MaxLevel-1))^(2^F67),0),D67+(E67-D67)*(1+G67)*((4-1)/(MaxLevel-1))^(2^F67)))</f>
+        <v/>
+      </c>
+      <c r="L67" s="13">
+        <f>IF(OR(D67="",E67=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C67,Stats!$A:$A,0)),FALSE),ROUND(D67+(E67-D67)*(1+G67)*((5-1)/(MaxLevel-1))^(2^F67),0),D67+(E67-D67)*(1+G67)*((5-1)/(MaxLevel-1))^(2^F67)))</f>
+        <v/>
+      </c>
+      <c r="M67" s="13">
+        <f>IF(OR(D67="",E67=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C67,Stats!$A:$A,0)),FALSE),ROUND(D67+(E67-D67)*(1+G67)*((6-1)/(MaxLevel-1))^(2^F67),0),D67+(E67-D67)*(1+G67)*((6-1)/(MaxLevel-1))^(2^F67)))</f>
+        <v/>
+      </c>
+      <c r="N67" s="13">
+        <f>IF(OR(D67="",E67=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C67,Stats!$A:$A,0)),FALSE),ROUND(D67+(E67-D67)*(1+G67)*((7-1)/(MaxLevel-1))^(2^F67),0),D67+(E67-D67)*(1+G67)*((7-1)/(MaxLevel-1))^(2^F67)))</f>
+        <v/>
+      </c>
+      <c r="O67" s="13">
+        <f>IF(OR(D67="",E67=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C67,Stats!$A:$A,0)),FALSE),ROUND(D67+(E67-D67)*(1+G67)*((8-1)/(MaxLevel-1))^(2^F67),0),D67+(E67-D67)*(1+G67)*((8-1)/(MaxLevel-1))^(2^F67)))</f>
+        <v/>
+      </c>
+      <c r="P67" s="13">
+        <f>IF(OR(D67="",E67=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C67,Stats!$A:$A,0)),FALSE),ROUND(D67+(E67-D67)*(1+G67)*((9-1)/(MaxLevel-1))^(2^F67),0),D67+(E67-D67)*(1+G67)*((9-1)/(MaxLevel-1))^(2^F67)))</f>
+        <v/>
+      </c>
+      <c r="Q67" s="13">
+        <f>IF(OR(D67="",E67=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C67,Stats!$A:$A,0)),FALSE),ROUND(D67+(E67-D67)*(1+G67)*((10-1)/(MaxLevel-1))^(2^F67),0),D67+(E67-D67)*(1+G67)*((10-1)/(MaxLevel-1))^(2^F67)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>01U</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>Resistance</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="n"/>
+      <c r="E68" s="5" t="n"/>
+      <c r="F68" s="5" t="n"/>
+      <c r="G68" s="5" t="n"/>
+      <c r="H68" s="13">
+        <f>IF(OR(D68="",E68=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C68,Stats!$A:$A,0)),FALSE),ROUND(D68+(E68-D68)*(1+G68)*((1-1)/(MaxLevel-1))^(2^F68),0),D68+(E68-D68)*(1+G68)*((1-1)/(MaxLevel-1))^(2^F68)))</f>
+        <v/>
+      </c>
+      <c r="I68" s="13">
+        <f>IF(OR(D68="",E68=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C68,Stats!$A:$A,0)),FALSE),ROUND(D68+(E68-D68)*(1+G68)*((2-1)/(MaxLevel-1))^(2^F68),0),D68+(E68-D68)*(1+G68)*((2-1)/(MaxLevel-1))^(2^F68)))</f>
+        <v/>
+      </c>
+      <c r="J68" s="13">
+        <f>IF(OR(D68="",E68=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C68,Stats!$A:$A,0)),FALSE),ROUND(D68+(E68-D68)*(1+G68)*((3-1)/(MaxLevel-1))^(2^F68),0),D68+(E68-D68)*(1+G68)*((3-1)/(MaxLevel-1))^(2^F68)))</f>
+        <v/>
+      </c>
+      <c r="K68" s="13">
+        <f>IF(OR(D68="",E68=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C68,Stats!$A:$A,0)),FALSE),ROUND(D68+(E68-D68)*(1+G68)*((4-1)/(MaxLevel-1))^(2^F68),0),D68+(E68-D68)*(1+G68)*((4-1)/(MaxLevel-1))^(2^F68)))</f>
+        <v/>
+      </c>
+      <c r="L68" s="13">
+        <f>IF(OR(D68="",E68=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C68,Stats!$A:$A,0)),FALSE),ROUND(D68+(E68-D68)*(1+G68)*((5-1)/(MaxLevel-1))^(2^F68),0),D68+(E68-D68)*(1+G68)*((5-1)/(MaxLevel-1))^(2^F68)))</f>
+        <v/>
+      </c>
+      <c r="M68" s="13">
+        <f>IF(OR(D68="",E68=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C68,Stats!$A:$A,0)),FALSE),ROUND(D68+(E68-D68)*(1+G68)*((6-1)/(MaxLevel-1))^(2^F68),0),D68+(E68-D68)*(1+G68)*((6-1)/(MaxLevel-1))^(2^F68)))</f>
+        <v/>
+      </c>
+      <c r="N68" s="13">
+        <f>IF(OR(D68="",E68=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C68,Stats!$A:$A,0)),FALSE),ROUND(D68+(E68-D68)*(1+G68)*((7-1)/(MaxLevel-1))^(2^F68),0),D68+(E68-D68)*(1+G68)*((7-1)/(MaxLevel-1))^(2^F68)))</f>
+        <v/>
+      </c>
+      <c r="O68" s="13">
+        <f>IF(OR(D68="",E68=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C68,Stats!$A:$A,0)),FALSE),ROUND(D68+(E68-D68)*(1+G68)*((8-1)/(MaxLevel-1))^(2^F68),0),D68+(E68-D68)*(1+G68)*((8-1)/(MaxLevel-1))^(2^F68)))</f>
+        <v/>
+      </c>
+      <c r="P68" s="13">
+        <f>IF(OR(D68="",E68=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C68,Stats!$A:$A,0)),FALSE),ROUND(D68+(E68-D68)*(1+G68)*((9-1)/(MaxLevel-1))^(2^F68),0),D68+(E68-D68)*(1+G68)*((9-1)/(MaxLevel-1))^(2^F68)))</f>
+        <v/>
+      </c>
+      <c r="Q68" s="13">
+        <f>IF(OR(D68="",E68=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C68,Stats!$A:$A,0)),FALSE),ROUND(D68+(E68-D68)*(1+G68)*((10-1)/(MaxLevel-1))^(2^F68),0),D68+(E68-D68)*(1+G68)*((10-1)/(MaxLevel-1))^(2^F68)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>01U</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>Luck</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="n"/>
+      <c r="E69" s="5" t="n"/>
+      <c r="F69" s="5" t="n"/>
+      <c r="G69" s="5" t="n"/>
+      <c r="H69" s="13">
+        <f>IF(OR(D69="",E69=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C69,Stats!$A:$A,0)),FALSE),ROUND(D69+(E69-D69)*(1+G69)*((1-1)/(MaxLevel-1))^(2^F69),0),D69+(E69-D69)*(1+G69)*((1-1)/(MaxLevel-1))^(2^F69)))</f>
+        <v/>
+      </c>
+      <c r="I69" s="13">
+        <f>IF(OR(D69="",E69=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C69,Stats!$A:$A,0)),FALSE),ROUND(D69+(E69-D69)*(1+G69)*((2-1)/(MaxLevel-1))^(2^F69),0),D69+(E69-D69)*(1+G69)*((2-1)/(MaxLevel-1))^(2^F69)))</f>
+        <v/>
+      </c>
+      <c r="J69" s="13">
+        <f>IF(OR(D69="",E69=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C69,Stats!$A:$A,0)),FALSE),ROUND(D69+(E69-D69)*(1+G69)*((3-1)/(MaxLevel-1))^(2^F69),0),D69+(E69-D69)*(1+G69)*((3-1)/(MaxLevel-1))^(2^F69)))</f>
+        <v/>
+      </c>
+      <c r="K69" s="13">
+        <f>IF(OR(D69="",E69=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C69,Stats!$A:$A,0)),FALSE),ROUND(D69+(E69-D69)*(1+G69)*((4-1)/(MaxLevel-1))^(2^F69),0),D69+(E69-D69)*(1+G69)*((4-1)/(MaxLevel-1))^(2^F69)))</f>
+        <v/>
+      </c>
+      <c r="L69" s="13">
+        <f>IF(OR(D69="",E69=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C69,Stats!$A:$A,0)),FALSE),ROUND(D69+(E69-D69)*(1+G69)*((5-1)/(MaxLevel-1))^(2^F69),0),D69+(E69-D69)*(1+G69)*((5-1)/(MaxLevel-1))^(2^F69)))</f>
+        <v/>
+      </c>
+      <c r="M69" s="13">
+        <f>IF(OR(D69="",E69=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C69,Stats!$A:$A,0)),FALSE),ROUND(D69+(E69-D69)*(1+G69)*((6-1)/(MaxLevel-1))^(2^F69),0),D69+(E69-D69)*(1+G69)*((6-1)/(MaxLevel-1))^(2^F69)))</f>
+        <v/>
+      </c>
+      <c r="N69" s="13">
+        <f>IF(OR(D69="",E69=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C69,Stats!$A:$A,0)),FALSE),ROUND(D69+(E69-D69)*(1+G69)*((7-1)/(MaxLevel-1))^(2^F69),0),D69+(E69-D69)*(1+G69)*((7-1)/(MaxLevel-1))^(2^F69)))</f>
+        <v/>
+      </c>
+      <c r="O69" s="13">
+        <f>IF(OR(D69="",E69=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C69,Stats!$A:$A,0)),FALSE),ROUND(D69+(E69-D69)*(1+G69)*((8-1)/(MaxLevel-1))^(2^F69),0),D69+(E69-D69)*(1+G69)*((8-1)/(MaxLevel-1))^(2^F69)))</f>
+        <v/>
+      </c>
+      <c r="P69" s="13">
+        <f>IF(OR(D69="",E69=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C69,Stats!$A:$A,0)),FALSE),ROUND(D69+(E69-D69)*(1+G69)*((9-1)/(MaxLevel-1))^(2^F69),0),D69+(E69-D69)*(1+G69)*((9-1)/(MaxLevel-1))^(2^F69)))</f>
+        <v/>
+      </c>
+      <c r="Q69" s="13">
+        <f>IF(OR(D69="",E69=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C69,Stats!$A:$A,0)),FALSE),ROUND(D69+(E69-D69)*(1+G69)*((10-1)/(MaxLevel-1))^(2^F69),0),D69+(E69-D69)*(1+G69)*((10-1)/(MaxLevel-1))^(2^F69)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>01U</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="n"/>
+      <c r="E70" s="5" t="n"/>
+      <c r="F70" s="5" t="n"/>
+      <c r="G70" s="5" t="n"/>
+      <c r="H70" s="13">
+        <f>IF(OR(D70="",E70=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C70,Stats!$A:$A,0)),FALSE),ROUND(D70+(E70-D70)*(1+G70)*((1-1)/(MaxLevel-1))^(2^F70),0),D70+(E70-D70)*(1+G70)*((1-1)/(MaxLevel-1))^(2^F70)))</f>
+        <v/>
+      </c>
+      <c r="I70" s="13">
+        <f>IF(OR(D70="",E70=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C70,Stats!$A:$A,0)),FALSE),ROUND(D70+(E70-D70)*(1+G70)*((2-1)/(MaxLevel-1))^(2^F70),0),D70+(E70-D70)*(1+G70)*((2-1)/(MaxLevel-1))^(2^F70)))</f>
+        <v/>
+      </c>
+      <c r="J70" s="13">
+        <f>IF(OR(D70="",E70=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C70,Stats!$A:$A,0)),FALSE),ROUND(D70+(E70-D70)*(1+G70)*((3-1)/(MaxLevel-1))^(2^F70),0),D70+(E70-D70)*(1+G70)*((3-1)/(MaxLevel-1))^(2^F70)))</f>
+        <v/>
+      </c>
+      <c r="K70" s="13">
+        <f>IF(OR(D70="",E70=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C70,Stats!$A:$A,0)),FALSE),ROUND(D70+(E70-D70)*(1+G70)*((4-1)/(MaxLevel-1))^(2^F70),0),D70+(E70-D70)*(1+G70)*((4-1)/(MaxLevel-1))^(2^F70)))</f>
+        <v/>
+      </c>
+      <c r="L70" s="13">
+        <f>IF(OR(D70="",E70=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C70,Stats!$A:$A,0)),FALSE),ROUND(D70+(E70-D70)*(1+G70)*((5-1)/(MaxLevel-1))^(2^F70),0),D70+(E70-D70)*(1+G70)*((5-1)/(MaxLevel-1))^(2^F70)))</f>
+        <v/>
+      </c>
+      <c r="M70" s="13">
+        <f>IF(OR(D70="",E70=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C70,Stats!$A:$A,0)),FALSE),ROUND(D70+(E70-D70)*(1+G70)*((6-1)/(MaxLevel-1))^(2^F70),0),D70+(E70-D70)*(1+G70)*((6-1)/(MaxLevel-1))^(2^F70)))</f>
+        <v/>
+      </c>
+      <c r="N70" s="13">
+        <f>IF(OR(D70="",E70=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C70,Stats!$A:$A,0)),FALSE),ROUND(D70+(E70-D70)*(1+G70)*((7-1)/(MaxLevel-1))^(2^F70),0),D70+(E70-D70)*(1+G70)*((7-1)/(MaxLevel-1))^(2^F70)))</f>
+        <v/>
+      </c>
+      <c r="O70" s="13">
+        <f>IF(OR(D70="",E70=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C70,Stats!$A:$A,0)),FALSE),ROUND(D70+(E70-D70)*(1+G70)*((8-1)/(MaxLevel-1))^(2^F70),0),D70+(E70-D70)*(1+G70)*((8-1)/(MaxLevel-1))^(2^F70)))</f>
+        <v/>
+      </c>
+      <c r="P70" s="13">
+        <f>IF(OR(D70="",E70=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C70,Stats!$A:$A,0)),FALSE),ROUND(D70+(E70-D70)*(1+G70)*((9-1)/(MaxLevel-1))^(2^F70),0),D70+(E70-D70)*(1+G70)*((9-1)/(MaxLevel-1))^(2^F70)))</f>
+        <v/>
+      </c>
+      <c r="Q70" s="13">
+        <f>IF(OR(D70="",E70=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C70,Stats!$A:$A,0)),FALSE),ROUND(D70+(E70-D70)*(1+G70)*((10-1)/(MaxLevel-1))^(2^F70),0),D70+(E70-D70)*(1+G70)*((10-1)/(MaxLevel-1))^(2^F70)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>01U</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>WorkingCost</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="n"/>
+      <c r="E71" s="5" t="n"/>
+      <c r="F71" s="5" t="n"/>
+      <c r="G71" s="5" t="n"/>
+      <c r="H71" s="13">
+        <f>IF(OR(D71="",E71=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C71,Stats!$A:$A,0)),FALSE),ROUND(D71+(E71-D71)*(1+G71)*((1-1)/(MaxLevel-1))^(2^F71),0),D71+(E71-D71)*(1+G71)*((1-1)/(MaxLevel-1))^(2^F71)))</f>
+        <v/>
+      </c>
+      <c r="I71" s="13">
+        <f>IF(OR(D71="",E71=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C71,Stats!$A:$A,0)),FALSE),ROUND(D71+(E71-D71)*(1+G71)*((2-1)/(MaxLevel-1))^(2^F71),0),D71+(E71-D71)*(1+G71)*((2-1)/(MaxLevel-1))^(2^F71)))</f>
+        <v/>
+      </c>
+      <c r="J71" s="13">
+        <f>IF(OR(D71="",E71=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C71,Stats!$A:$A,0)),FALSE),ROUND(D71+(E71-D71)*(1+G71)*((3-1)/(MaxLevel-1))^(2^F71),0),D71+(E71-D71)*(1+G71)*((3-1)/(MaxLevel-1))^(2^F71)))</f>
+        <v/>
+      </c>
+      <c r="K71" s="13">
+        <f>IF(OR(D71="",E71=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C71,Stats!$A:$A,0)),FALSE),ROUND(D71+(E71-D71)*(1+G71)*((4-1)/(MaxLevel-1))^(2^F71),0),D71+(E71-D71)*(1+G71)*((4-1)/(MaxLevel-1))^(2^F71)))</f>
+        <v/>
+      </c>
+      <c r="L71" s="13">
+        <f>IF(OR(D71="",E71=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C71,Stats!$A:$A,0)),FALSE),ROUND(D71+(E71-D71)*(1+G71)*((5-1)/(MaxLevel-1))^(2^F71),0),D71+(E71-D71)*(1+G71)*((5-1)/(MaxLevel-1))^(2^F71)))</f>
+        <v/>
+      </c>
+      <c r="M71" s="13">
+        <f>IF(OR(D71="",E71=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C71,Stats!$A:$A,0)),FALSE),ROUND(D71+(E71-D71)*(1+G71)*((6-1)/(MaxLevel-1))^(2^F71),0),D71+(E71-D71)*(1+G71)*((6-1)/(MaxLevel-1))^(2^F71)))</f>
+        <v/>
+      </c>
+      <c r="N71" s="13">
+        <f>IF(OR(D71="",E71=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C71,Stats!$A:$A,0)),FALSE),ROUND(D71+(E71-D71)*(1+G71)*((7-1)/(MaxLevel-1))^(2^F71),0),D71+(E71-D71)*(1+G71)*((7-1)/(MaxLevel-1))^(2^F71)))</f>
+        <v/>
+      </c>
+      <c r="O71" s="13">
+        <f>IF(OR(D71="",E71=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C71,Stats!$A:$A,0)),FALSE),ROUND(D71+(E71-D71)*(1+G71)*((8-1)/(MaxLevel-1))^(2^F71),0),D71+(E71-D71)*(1+G71)*((8-1)/(MaxLevel-1))^(2^F71)))</f>
+        <v/>
+      </c>
+      <c r="P71" s="13">
+        <f>IF(OR(D71="",E71=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C71,Stats!$A:$A,0)),FALSE),ROUND(D71+(E71-D71)*(1+G71)*((9-1)/(MaxLevel-1))^(2^F71),0),D71+(E71-D71)*(1+G71)*((9-1)/(MaxLevel-1))^(2^F71)))</f>
+        <v/>
+      </c>
+      <c r="Q71" s="13">
+        <f>IF(OR(D71="",E71=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C71,Stats!$A:$A,0)),FALSE),ROUND(D71+(E71-D71)*(1+G71)*((10-1)/(MaxLevel-1))^(2^F71),0),D71+(E71-D71)*(1+G71)*((10-1)/(MaxLevel-1))^(2^F71)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>01U</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>SkillResearch</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="n"/>
+      <c r="E72" s="5" t="n"/>
+      <c r="F72" s="5" t="n"/>
+      <c r="G72" s="5" t="n"/>
+      <c r="H72" s="13">
+        <f>IF(OR(D72="",E72=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C72,Stats!$A:$A,0)),FALSE),ROUND(D72+(E72-D72)*(1+G72)*((1-1)/(MaxLevel-1))^(2^F72),0),D72+(E72-D72)*(1+G72)*((1-1)/(MaxLevel-1))^(2^F72)))</f>
+        <v/>
+      </c>
+      <c r="I72" s="13">
+        <f>IF(OR(D72="",E72=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C72,Stats!$A:$A,0)),FALSE),ROUND(D72+(E72-D72)*(1+G72)*((2-1)/(MaxLevel-1))^(2^F72),0),D72+(E72-D72)*(1+G72)*((2-1)/(MaxLevel-1))^(2^F72)))</f>
+        <v/>
+      </c>
+      <c r="J72" s="13">
+        <f>IF(OR(D72="",E72=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C72,Stats!$A:$A,0)),FALSE),ROUND(D72+(E72-D72)*(1+G72)*((3-1)/(MaxLevel-1))^(2^F72),0),D72+(E72-D72)*(1+G72)*((3-1)/(MaxLevel-1))^(2^F72)))</f>
+        <v/>
+      </c>
+      <c r="K72" s="13">
+        <f>IF(OR(D72="",E72=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C72,Stats!$A:$A,0)),FALSE),ROUND(D72+(E72-D72)*(1+G72)*((4-1)/(MaxLevel-1))^(2^F72),0),D72+(E72-D72)*(1+G72)*((4-1)/(MaxLevel-1))^(2^F72)))</f>
+        <v/>
+      </c>
+      <c r="L72" s="13">
+        <f>IF(OR(D72="",E72=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C72,Stats!$A:$A,0)),FALSE),ROUND(D72+(E72-D72)*(1+G72)*((5-1)/(MaxLevel-1))^(2^F72),0),D72+(E72-D72)*(1+G72)*((5-1)/(MaxLevel-1))^(2^F72)))</f>
+        <v/>
+      </c>
+      <c r="M72" s="13">
+        <f>IF(OR(D72="",E72=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C72,Stats!$A:$A,0)),FALSE),ROUND(D72+(E72-D72)*(1+G72)*((6-1)/(MaxLevel-1))^(2^F72),0),D72+(E72-D72)*(1+G72)*((6-1)/(MaxLevel-1))^(2^F72)))</f>
+        <v/>
+      </c>
+      <c r="N72" s="13">
+        <f>IF(OR(D72="",E72=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C72,Stats!$A:$A,0)),FALSE),ROUND(D72+(E72-D72)*(1+G72)*((7-1)/(MaxLevel-1))^(2^F72),0),D72+(E72-D72)*(1+G72)*((7-1)/(MaxLevel-1))^(2^F72)))</f>
+        <v/>
+      </c>
+      <c r="O72" s="13">
+        <f>IF(OR(D72="",E72=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C72,Stats!$A:$A,0)),FALSE),ROUND(D72+(E72-D72)*(1+G72)*((8-1)/(MaxLevel-1))^(2^F72),0),D72+(E72-D72)*(1+G72)*((8-1)/(MaxLevel-1))^(2^F72)))</f>
+        <v/>
+      </c>
+      <c r="P72" s="13">
+        <f>IF(OR(D72="",E72=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C72,Stats!$A:$A,0)),FALSE),ROUND(D72+(E72-D72)*(1+G72)*((9-1)/(MaxLevel-1))^(2^F72),0),D72+(E72-D72)*(1+G72)*((9-1)/(MaxLevel-1))^(2^F72)))</f>
+        <v/>
+      </c>
+      <c r="Q72" s="13">
+        <f>IF(OR(D72="",E72=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C72,Stats!$A:$A,0)),FALSE),ROUND(D72+(E72-D72)*(1+G72)*((10-1)/(MaxLevel-1))^(2^F72),0),D72+(E72-D72)*(1+G72)*((10-1)/(MaxLevel-1))^(2^F72)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>01U</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>SkillTrain</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="n"/>
+      <c r="E73" s="5" t="n"/>
+      <c r="F73" s="5" t="n"/>
+      <c r="G73" s="5" t="n"/>
+      <c r="H73" s="13">
+        <f>IF(OR(D73="",E73=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C73,Stats!$A:$A,0)),FALSE),ROUND(D73+(E73-D73)*(1+G73)*((1-1)/(MaxLevel-1))^(2^F73),0),D73+(E73-D73)*(1+G73)*((1-1)/(MaxLevel-1))^(2^F73)))</f>
+        <v/>
+      </c>
+      <c r="I73" s="13">
+        <f>IF(OR(D73="",E73=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C73,Stats!$A:$A,0)),FALSE),ROUND(D73+(E73-D73)*(1+G73)*((2-1)/(MaxLevel-1))^(2^F73),0),D73+(E73-D73)*(1+G73)*((2-1)/(MaxLevel-1))^(2^F73)))</f>
+        <v/>
+      </c>
+      <c r="J73" s="13">
+        <f>IF(OR(D73="",E73=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C73,Stats!$A:$A,0)),FALSE),ROUND(D73+(E73-D73)*(1+G73)*((3-1)/(MaxLevel-1))^(2^F73),0),D73+(E73-D73)*(1+G73)*((3-1)/(MaxLevel-1))^(2^F73)))</f>
+        <v/>
+      </c>
+      <c r="K73" s="13">
+        <f>IF(OR(D73="",E73=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C73,Stats!$A:$A,0)),FALSE),ROUND(D73+(E73-D73)*(1+G73)*((4-1)/(MaxLevel-1))^(2^F73),0),D73+(E73-D73)*(1+G73)*((4-1)/(MaxLevel-1))^(2^F73)))</f>
+        <v/>
+      </c>
+      <c r="L73" s="13">
+        <f>IF(OR(D73="",E73=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C73,Stats!$A:$A,0)),FALSE),ROUND(D73+(E73-D73)*(1+G73)*((5-1)/(MaxLevel-1))^(2^F73),0),D73+(E73-D73)*(1+G73)*((5-1)/(MaxLevel-1))^(2^F73)))</f>
+        <v/>
+      </c>
+      <c r="M73" s="13">
+        <f>IF(OR(D73="",E73=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C73,Stats!$A:$A,0)),FALSE),ROUND(D73+(E73-D73)*(1+G73)*((6-1)/(MaxLevel-1))^(2^F73),0),D73+(E73-D73)*(1+G73)*((6-1)/(MaxLevel-1))^(2^F73)))</f>
+        <v/>
+      </c>
+      <c r="N73" s="13">
+        <f>IF(OR(D73="",E73=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C73,Stats!$A:$A,0)),FALSE),ROUND(D73+(E73-D73)*(1+G73)*((7-1)/(MaxLevel-1))^(2^F73),0),D73+(E73-D73)*(1+G73)*((7-1)/(MaxLevel-1))^(2^F73)))</f>
+        <v/>
+      </c>
+      <c r="O73" s="13">
+        <f>IF(OR(D73="",E73=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C73,Stats!$A:$A,0)),FALSE),ROUND(D73+(E73-D73)*(1+G73)*((8-1)/(MaxLevel-1))^(2^F73),0),D73+(E73-D73)*(1+G73)*((8-1)/(MaxLevel-1))^(2^F73)))</f>
+        <v/>
+      </c>
+      <c r="P73" s="13">
+        <f>IF(OR(D73="",E73=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C73,Stats!$A:$A,0)),FALSE),ROUND(D73+(E73-D73)*(1+G73)*((9-1)/(MaxLevel-1))^(2^F73),0),D73+(E73-D73)*(1+G73)*((9-1)/(MaxLevel-1))^(2^F73)))</f>
+        <v/>
+      </c>
+      <c r="Q73" s="13">
+        <f>IF(OR(D73="",E73=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C73,Stats!$A:$A,0)),FALSE),ROUND(D73+(E73-D73)*(1+G73)*((10-1)/(MaxLevel-1))^(2^F73),0),D73+(E73-D73)*(1+G73)*((10-1)/(MaxLevel-1))^(2^F73)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>01U</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>SkillBuild</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="13">
+        <f>IF(OR(D74="",E74=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C74,Stats!$A:$A,0)),FALSE),ROUND(D74+(E74-D74)*(1+G74)*((1-1)/(MaxLevel-1))^(2^F74),0),D74+(E74-D74)*(1+G74)*((1-1)/(MaxLevel-1))^(2^F74)))</f>
+        <v/>
+      </c>
+      <c r="I74" s="13">
+        <f>IF(OR(D74="",E74=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C74,Stats!$A:$A,0)),FALSE),ROUND(D74+(E74-D74)*(1+G74)*((2-1)/(MaxLevel-1))^(2^F74),0),D74+(E74-D74)*(1+G74)*((2-1)/(MaxLevel-1))^(2^F74)))</f>
+        <v/>
+      </c>
+      <c r="J74" s="13">
+        <f>IF(OR(D74="",E74=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C74,Stats!$A:$A,0)),FALSE),ROUND(D74+(E74-D74)*(1+G74)*((3-1)/(MaxLevel-1))^(2^F74),0),D74+(E74-D74)*(1+G74)*((3-1)/(MaxLevel-1))^(2^F74)))</f>
+        <v/>
+      </c>
+      <c r="K74" s="13">
+        <f>IF(OR(D74="",E74=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C74,Stats!$A:$A,0)),FALSE),ROUND(D74+(E74-D74)*(1+G74)*((4-1)/(MaxLevel-1))^(2^F74),0),D74+(E74-D74)*(1+G74)*((4-1)/(MaxLevel-1))^(2^F74)))</f>
+        <v/>
+      </c>
+      <c r="L74" s="13">
+        <f>IF(OR(D74="",E74=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C74,Stats!$A:$A,0)),FALSE),ROUND(D74+(E74-D74)*(1+G74)*((5-1)/(MaxLevel-1))^(2^F74),0),D74+(E74-D74)*(1+G74)*((5-1)/(MaxLevel-1))^(2^F74)))</f>
+        <v/>
+      </c>
+      <c r="M74" s="13">
+        <f>IF(OR(D74="",E74=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C74,Stats!$A:$A,0)),FALSE),ROUND(D74+(E74-D74)*(1+G74)*((6-1)/(MaxLevel-1))^(2^F74),0),D74+(E74-D74)*(1+G74)*((6-1)/(MaxLevel-1))^(2^F74)))</f>
+        <v/>
+      </c>
+      <c r="N74" s="13">
+        <f>IF(OR(D74="",E74=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C74,Stats!$A:$A,0)),FALSE),ROUND(D74+(E74-D74)*(1+G74)*((7-1)/(MaxLevel-1))^(2^F74),0),D74+(E74-D74)*(1+G74)*((7-1)/(MaxLevel-1))^(2^F74)))</f>
+        <v/>
+      </c>
+      <c r="O74" s="13">
+        <f>IF(OR(D74="",E74=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C74,Stats!$A:$A,0)),FALSE),ROUND(D74+(E74-D74)*(1+G74)*((8-1)/(MaxLevel-1))^(2^F74),0),D74+(E74-D74)*(1+G74)*((8-1)/(MaxLevel-1))^(2^F74)))</f>
+        <v/>
+      </c>
+      <c r="P74" s="13">
+        <f>IF(OR(D74="",E74=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C74,Stats!$A:$A,0)),FALSE),ROUND(D74+(E74-D74)*(1+G74)*((9-1)/(MaxLevel-1))^(2^F74),0),D74+(E74-D74)*(1+G74)*((9-1)/(MaxLevel-1))^(2^F74)))</f>
+        <v/>
+      </c>
+      <c r="Q74" s="13">
+        <f>IF(OR(D74="",E74=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C74,Stats!$A:$A,0)),FALSE),ROUND(D74+(E74-D74)*(1+G74)*((10-1)/(MaxLevel-1))^(2^F74),0),D74+(E74-D74)*(1+G74)*((10-1)/(MaxLevel-1))^(2^F74)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>01U</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>SkillPray</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="n"/>
+      <c r="E75" s="5" t="n"/>
+      <c r="F75" s="5" t="n"/>
+      <c r="G75" s="5" t="n"/>
+      <c r="H75" s="13">
+        <f>IF(OR(D75="",E75=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C75,Stats!$A:$A,0)),FALSE),ROUND(D75+(E75-D75)*(1+G75)*((1-1)/(MaxLevel-1))^(2^F75),0),D75+(E75-D75)*(1+G75)*((1-1)/(MaxLevel-1))^(2^F75)))</f>
+        <v/>
+      </c>
+      <c r="I75" s="13">
+        <f>IF(OR(D75="",E75=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C75,Stats!$A:$A,0)),FALSE),ROUND(D75+(E75-D75)*(1+G75)*((2-1)/(MaxLevel-1))^(2^F75),0),D75+(E75-D75)*(1+G75)*((2-1)/(MaxLevel-1))^(2^F75)))</f>
+        <v/>
+      </c>
+      <c r="J75" s="13">
+        <f>IF(OR(D75="",E75=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C75,Stats!$A:$A,0)),FALSE),ROUND(D75+(E75-D75)*(1+G75)*((3-1)/(MaxLevel-1))^(2^F75),0),D75+(E75-D75)*(1+G75)*((3-1)/(MaxLevel-1))^(2^F75)))</f>
+        <v/>
+      </c>
+      <c r="K75" s="13">
+        <f>IF(OR(D75="",E75=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C75,Stats!$A:$A,0)),FALSE),ROUND(D75+(E75-D75)*(1+G75)*((4-1)/(MaxLevel-1))^(2^F75),0),D75+(E75-D75)*(1+G75)*((4-1)/(MaxLevel-1))^(2^F75)))</f>
+        <v/>
+      </c>
+      <c r="L75" s="13">
+        <f>IF(OR(D75="",E75=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C75,Stats!$A:$A,0)),FALSE),ROUND(D75+(E75-D75)*(1+G75)*((5-1)/(MaxLevel-1))^(2^F75),0),D75+(E75-D75)*(1+G75)*((5-1)/(MaxLevel-1))^(2^F75)))</f>
+        <v/>
+      </c>
+      <c r="M75" s="13">
+        <f>IF(OR(D75="",E75=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C75,Stats!$A:$A,0)),FALSE),ROUND(D75+(E75-D75)*(1+G75)*((6-1)/(MaxLevel-1))^(2^F75),0),D75+(E75-D75)*(1+G75)*((6-1)/(MaxLevel-1))^(2^F75)))</f>
+        <v/>
+      </c>
+      <c r="N75" s="13">
+        <f>IF(OR(D75="",E75=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C75,Stats!$A:$A,0)),FALSE),ROUND(D75+(E75-D75)*(1+G75)*((7-1)/(MaxLevel-1))^(2^F75),0),D75+(E75-D75)*(1+G75)*((7-1)/(MaxLevel-1))^(2^F75)))</f>
+        <v/>
+      </c>
+      <c r="O75" s="13">
+        <f>IF(OR(D75="",E75=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C75,Stats!$A:$A,0)),FALSE),ROUND(D75+(E75-D75)*(1+G75)*((8-1)/(MaxLevel-1))^(2^F75),0),D75+(E75-D75)*(1+G75)*((8-1)/(MaxLevel-1))^(2^F75)))</f>
+        <v/>
+      </c>
+      <c r="P75" s="13">
+        <f>IF(OR(D75="",E75=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C75,Stats!$A:$A,0)),FALSE),ROUND(D75+(E75-D75)*(1+G75)*((9-1)/(MaxLevel-1))^(2^F75),0),D75+(E75-D75)*(1+G75)*((9-1)/(MaxLevel-1))^(2^F75)))</f>
+        <v/>
+      </c>
+      <c r="Q75" s="13">
+        <f>IF(OR(D75="",E75=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C75,Stats!$A:$A,0)),FALSE),ROUND(D75+(E75-D75)*(1+G75)*((10-1)/(MaxLevel-1))^(2^F75),0),D75+(E75-D75)*(1+G75)*((10-1)/(MaxLevel-1))^(2^F75)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>01U</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>SkillTorture</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="n"/>
+      <c r="E76" s="5" t="n"/>
+      <c r="F76" s="5" t="n"/>
+      <c r="G76" s="5" t="n"/>
+      <c r="H76" s="13">
+        <f>IF(OR(D76="",E76=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C76,Stats!$A:$A,0)),FALSE),ROUND(D76+(E76-D76)*(1+G76)*((1-1)/(MaxLevel-1))^(2^F76),0),D76+(E76-D76)*(1+G76)*((1-1)/(MaxLevel-1))^(2^F76)))</f>
+        <v/>
+      </c>
+      <c r="I76" s="13">
+        <f>IF(OR(D76="",E76=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C76,Stats!$A:$A,0)),FALSE),ROUND(D76+(E76-D76)*(1+G76)*((2-1)/(MaxLevel-1))^(2^F76),0),D76+(E76-D76)*(1+G76)*((2-1)/(MaxLevel-1))^(2^F76)))</f>
+        <v/>
+      </c>
+      <c r="J76" s="13">
+        <f>IF(OR(D76="",E76=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C76,Stats!$A:$A,0)),FALSE),ROUND(D76+(E76-D76)*(1+G76)*((3-1)/(MaxLevel-1))^(2^F76),0),D76+(E76-D76)*(1+G76)*((3-1)/(MaxLevel-1))^(2^F76)))</f>
+        <v/>
+      </c>
+      <c r="K76" s="13">
+        <f>IF(OR(D76="",E76=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C76,Stats!$A:$A,0)),FALSE),ROUND(D76+(E76-D76)*(1+G76)*((4-1)/(MaxLevel-1))^(2^F76),0),D76+(E76-D76)*(1+G76)*((4-1)/(MaxLevel-1))^(2^F76)))</f>
+        <v/>
+      </c>
+      <c r="L76" s="13">
+        <f>IF(OR(D76="",E76=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C76,Stats!$A:$A,0)),FALSE),ROUND(D76+(E76-D76)*(1+G76)*((5-1)/(MaxLevel-1))^(2^F76),0),D76+(E76-D76)*(1+G76)*((5-1)/(MaxLevel-1))^(2^F76)))</f>
+        <v/>
+      </c>
+      <c r="M76" s="13">
+        <f>IF(OR(D76="",E76=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C76,Stats!$A:$A,0)),FALSE),ROUND(D76+(E76-D76)*(1+G76)*((6-1)/(MaxLevel-1))^(2^F76),0),D76+(E76-D76)*(1+G76)*((6-1)/(MaxLevel-1))^(2^F76)))</f>
+        <v/>
+      </c>
+      <c r="N76" s="13">
+        <f>IF(OR(D76="",E76=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C76,Stats!$A:$A,0)),FALSE),ROUND(D76+(E76-D76)*(1+G76)*((7-1)/(MaxLevel-1))^(2^F76),0),D76+(E76-D76)*(1+G76)*((7-1)/(MaxLevel-1))^(2^F76)))</f>
+        <v/>
+      </c>
+      <c r="O76" s="13">
+        <f>IF(OR(D76="",E76=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C76,Stats!$A:$A,0)),FALSE),ROUND(D76+(E76-D76)*(1+G76)*((8-1)/(MaxLevel-1))^(2^F76),0),D76+(E76-D76)*(1+G76)*((8-1)/(MaxLevel-1))^(2^F76)))</f>
+        <v/>
+      </c>
+      <c r="P76" s="13">
+        <f>IF(OR(D76="",E76=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C76,Stats!$A:$A,0)),FALSE),ROUND(D76+(E76-D76)*(1+G76)*((9-1)/(MaxLevel-1))^(2^F76),0),D76+(E76-D76)*(1+G76)*((9-1)/(MaxLevel-1))^(2^F76)))</f>
+        <v/>
+      </c>
+      <c r="Q76" s="13">
+        <f>IF(OR(D76="",E76=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C76,Stats!$A:$A,0)),FALSE),ROUND(D76+(E76-D76)*(1+G76)*((10-1)/(MaxLevel-1))^(2^F76),0),D76+(E76-D76)*(1+G76)*((10-1)/(MaxLevel-1))^(2^F76)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>01U</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>Anger</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="n"/>
+      <c r="E77" s="5" t="n"/>
+      <c r="F77" s="5" t="n"/>
+      <c r="G77" s="5" t="n"/>
+      <c r="H77" s="13">
+        <f>IF(OR(D77="",E77=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C77,Stats!$A:$A,0)),FALSE),ROUND(D77+(E77-D77)*(1+G77)*((1-1)/(MaxLevel-1))^(2^F77),0),D77+(E77-D77)*(1+G77)*((1-1)/(MaxLevel-1))^(2^F77)))</f>
+        <v/>
+      </c>
+      <c r="I77" s="13">
+        <f>IF(OR(D77="",E77=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C77,Stats!$A:$A,0)),FALSE),ROUND(D77+(E77-D77)*(1+G77)*((2-1)/(MaxLevel-1))^(2^F77),0),D77+(E77-D77)*(1+G77)*((2-1)/(MaxLevel-1))^(2^F77)))</f>
+        <v/>
+      </c>
+      <c r="J77" s="13">
+        <f>IF(OR(D77="",E77=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C77,Stats!$A:$A,0)),FALSE),ROUND(D77+(E77-D77)*(1+G77)*((3-1)/(MaxLevel-1))^(2^F77),0),D77+(E77-D77)*(1+G77)*((3-1)/(MaxLevel-1))^(2^F77)))</f>
+        <v/>
+      </c>
+      <c r="K77" s="13">
+        <f>IF(OR(D77="",E77=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C77,Stats!$A:$A,0)),FALSE),ROUND(D77+(E77-D77)*(1+G77)*((4-1)/(MaxLevel-1))^(2^F77),0),D77+(E77-D77)*(1+G77)*((4-1)/(MaxLevel-1))^(2^F77)))</f>
+        <v/>
+      </c>
+      <c r="L77" s="13">
+        <f>IF(OR(D77="",E77=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C77,Stats!$A:$A,0)),FALSE),ROUND(D77+(E77-D77)*(1+G77)*((5-1)/(MaxLevel-1))^(2^F77),0),D77+(E77-D77)*(1+G77)*((5-1)/(MaxLevel-1))^(2^F77)))</f>
+        <v/>
+      </c>
+      <c r="M77" s="13">
+        <f>IF(OR(D77="",E77=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C77,Stats!$A:$A,0)),FALSE),ROUND(D77+(E77-D77)*(1+G77)*((6-1)/(MaxLevel-1))^(2^F77),0),D77+(E77-D77)*(1+G77)*((6-1)/(MaxLevel-1))^(2^F77)))</f>
+        <v/>
+      </c>
+      <c r="N77" s="13">
+        <f>IF(OR(D77="",E77=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C77,Stats!$A:$A,0)),FALSE),ROUND(D77+(E77-D77)*(1+G77)*((7-1)/(MaxLevel-1))^(2^F77),0),D77+(E77-D77)*(1+G77)*((7-1)/(MaxLevel-1))^(2^F77)))</f>
+        <v/>
+      </c>
+      <c r="O77" s="13">
+        <f>IF(OR(D77="",E77=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C77,Stats!$A:$A,0)),FALSE),ROUND(D77+(E77-D77)*(1+G77)*((8-1)/(MaxLevel-1))^(2^F77),0),D77+(E77-D77)*(1+G77)*((8-1)/(MaxLevel-1))^(2^F77)))</f>
+        <v/>
+      </c>
+      <c r="P77" s="13">
+        <f>IF(OR(D77="",E77=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C77,Stats!$A:$A,0)),FALSE),ROUND(D77+(E77-D77)*(1+G77)*((9-1)/(MaxLevel-1))^(2^F77),0),D77+(E77-D77)*(1+G77)*((9-1)/(MaxLevel-1))^(2^F77)))</f>
+        <v/>
+      </c>
+      <c r="Q77" s="13">
+        <f>IF(OR(D77="",E77=""),"",IF(IFERROR(INDEX(Stats!$D:$D,MATCH($C77,Stats!$A:$A,0)),FALSE),ROUND(D77+(E77-D77)*(1+G77)*((10-1)/(MaxLevel-1))^(2^F77),0),D77+(E77-D77)*(1+G77)*((10-1)/(MaxLevel-1))^(2^F77)))</f>
         <v/>
       </c>
     </row>

--- a/Data/MinionData.xlsx
+++ b/Data/MinionData.xlsx
@@ -872,25 +872,30 @@
     </comment>
     <comment ref="AE1" authorId="0" shapeId="0">
       <text>
-        <t>Relative pick chance among minions that currently qualify. Blank = 1.</t>
+        <t>TRUE = once it has reported for duty, this minion digs, claims, reinforces and hauls gold like a worker. Blank = FALSE. Worker-stance minions always do worker jobs.</t>
       </text>
     </comment>
     <comment ref="AF1" authorId="0" shapeId="0">
       <text>
-        <t>Population slots used. Blank = 1.</t>
+        <t>Relative pick chance among minions that currently qualify. Blank = 1.</t>
       </text>
     </comment>
     <comment ref="AG1" authorId="0" shapeId="0">
       <text>
-        <t>Room types that must be built (semicolon list), e.g. RoomA;RoomB.</t>
+        <t>Population slots used. Blank = 1.</t>
       </text>
     </comment>
     <comment ref="AH1" authorId="0" shapeId="0">
       <text>
+        <t>Room types that must be built (semicolon list), e.g. RoomA;RoomB.</t>
+      </text>
+    </comment>
+    <comment ref="AI1" authorId="0" shapeId="0">
+      <text>
         <t>Minimum size of each required room in tiles – same order as RequiredRooms, e.g. 9;4. Blank = any size.</t>
       </text>
     </comment>
-    <comment ref="AI1" authorId="0" shapeId="0">
+    <comment ref="AJ1" authorId="0" shapeId="0">
       <text>
         <t>Research IDs that must be complete (semicolon list).</t>
       </text>
@@ -3227,7 +3232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI5"/>
+  <dimension ref="A1:AJ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3260,11 +3265,12 @@
     <col width="12" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
-    <col width="14" customWidth="1" min="31" max="31"/>
-    <col width="16" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="14" customWidth="1" min="32" max="32"/>
     <col width="16" customWidth="1" min="33" max="33"/>
-    <col width="14" customWidth="1" min="34" max="34"/>
-    <col width="18" customWidth="1" min="35" max="35"/>
+    <col width="16" customWidth="1" min="34" max="34"/>
+    <col width="14" customWidth="1" min="35" max="35"/>
+    <col width="18" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3420,25 +3426,30 @@
       </c>
       <c r="AE1" s="3" t="inlineStr">
         <is>
+          <t>WorkerJobs</t>
+        </is>
+      </c>
+      <c r="AF1" s="3" t="inlineStr">
+        <is>
           <t>SummonWeight</t>
         </is>
       </c>
-      <c r="AF1" s="3" t="inlineStr">
+      <c r="AG1" s="3" t="inlineStr">
         <is>
           <t>PopulationCost</t>
         </is>
       </c>
-      <c r="AG1" s="3" t="inlineStr">
+      <c r="AH1" s="3" t="inlineStr">
         <is>
           <t>RequiredRooms</t>
         </is>
       </c>
-      <c r="AH1" s="3" t="inlineStr">
+      <c r="AI1" s="3" t="inlineStr">
         <is>
           <t>MinRoomTiles</t>
         </is>
       </c>
-      <c r="AI1" s="3" t="inlineStr">
+      <c r="AJ1" s="3" t="inlineStr">
         <is>
           <t>RequiredResearch</t>
         </is>
@@ -3528,6 +3539,7 @@
       <c r="AG2" s="4" t="n"/>
       <c r="AH2" s="4" t="n"/>
       <c r="AI2" s="4" t="n"/>
+      <c r="AJ2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -3610,21 +3622,22 @@
       <c r="AD3" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="AE3" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE3" s="4" t="n"/>
       <c r="AF3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="AG3" s="4" t="inlineStr">
+      <c r="AG3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH3" s="4" t="inlineStr">
         <is>
           <t>RoomA</t>
         </is>
       </c>
-      <c r="AH3" s="4" t="n">
+      <c r="AI3" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="AI3" s="4" t="n"/>
+      <c r="AJ3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -3707,23 +3720,26 @@
       <c r="AD4" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="AE4" s="4" t="n">
+      <c r="AE4" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="4" t="n">
         <v>0.6</v>
       </c>
-      <c r="AF4" s="4" t="n">
+      <c r="AG4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="AG4" s="4" t="inlineStr">
+      <c r="AH4" s="4" t="inlineStr">
         <is>
           <t>RoomA;RoomB</t>
         </is>
       </c>
-      <c r="AH4" s="4" t="inlineStr">
+      <c r="AI4" s="4" t="inlineStr">
         <is>
           <t>9;4</t>
         </is>
       </c>
-      <c r="AI4" s="4" t="inlineStr">
+      <c r="AJ4" s="4" t="inlineStr">
         <is>
           <t>Labyrinths</t>
         </is>
@@ -3795,6 +3811,7 @@
       <c r="AG5" s="4" t="n"/>
       <c r="AH5" s="4" t="n"/>
       <c r="AI5" s="4" t="n"/>
+      <c r="AJ5" s="4" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">

--- a/Data/MinionData.xlsx
+++ b/Data/MinionData.xlsx
@@ -1337,7 +1337,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>The Worker row (W) is the faction's imp. Imps read Health (max health), Strength (dig damage per second) and SkillBuild (claim/reinforce speed, 1 = normal) at their level; any of these left off the _Levels sheet keeps the imp prefab's own value.</t>
+          <t>The Worker row (W) is the faction's worker, placed by WorkerSpawner. Workers read Health (max health), Strength (dig damage per second) and SkillBuild (claim/reinforce speed, 1 = normal) at their level; any of these left off the _Levels sheet keeps the template's own value. Set WorkerJobs on any other minion to have it do worker jobs too.</t>
         </is>
       </c>
     </row>
